--- a/extenbooks/XS2101_extenbook.xlsx
+++ b/extenbooks/XS2101_extenbook.xlsx
@@ -998,14 +998,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="B12" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>XS2101-avg_CI_upper_bound</t>
+          <t>XS2101-avg_CI_lower_bound</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1024,11 +1024,11 @@
         <v>2002</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>XS2101-max_bienenfeld_deviation_pct</t>
+          <t>XS2101-avg_CI_upper_bound</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>dimensionless</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>XS2101-n_prices_switching_bienenfeld</t>
+          <t>XS2101-avg_CI_upper_bound</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>dimensionless</t>
         </is>
       </c>
     </row>
@@ -1070,11 +1070,11 @@
         <v>2002</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>XS2101-n_prices_switching_bienenfeld_pct</t>
+          <t>XS2101-max_bienenfeld_deviation_pct</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1093,11 +1093,11 @@
         <v>2002</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>XS2101-n_prices_switching_value</t>
+          <t>XS2101-n_prices_switching_bienenfeld</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1116,11 +1116,11 @@
         <v>2002</v>
       </c>
       <c r="B17" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XS2101-n_prices_switching_value_pct</t>
+          <t>XS2101-n_prices_switching_bienenfeld_pct</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1139,11 +1139,11 @@
         <v>2002</v>
       </c>
       <c r="B18" t="n">
-        <v>425</v>
+        <v>26</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XS2101-n_prices_total</t>
+          <t>XS2101-n_prices_switching_value</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1159,14 +1159,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B19" t="n">
-        <v>0.03</v>
+        <v>6.1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>XS2101-avg_CI_lower_bound</t>
+          <t>XS2101-n_prices_switching_value_pct</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1176,20 +1176,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>percent</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06</v>
+        <v>425</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XS2101-avg_CI_upper_bound</t>
+          <t>XS2101-n_prices_total</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A146"/>
+  <dimension ref="A1:A153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1254,42 +1254,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: XS2101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: XS2101</t>
+          <t>**Content type**: `derived`</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Content type**: `derived`</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: study_complete</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-fanout-ES</t>
+          <t>This series was previously catalogued under the identifier ES2101.</t>
         </is>
       </c>
     </row>
@@ -1323,107 +1319,111 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EJEEP 17(2): 265-275. The paper computes the Curvature Index (CI) and</t>
+          <t>EJEEP 17(2): 265-275. Sraffa prices are production prices derived from</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Theil index distributions across 295 aggregations of US BEA Benchmark</t>
+          <t>an economy's input-output structure. The paper computes the **Curvature</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IO matrices for 2002 and 2007.</t>
+          <t>Index (CI)** distributions and the **label-switching statistics** (share</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>of prices that switch sign relative to their labor value, and share that</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>For v1.0, XS2101 ships the verbatim named summary statistics quoted in</t>
+          <t>switch relative to the Bienenfeld line) across 295 aggregations of US</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>paper Section 5 (p. 272). The full ~295-point CI/Theil scatters</t>
+          <t>input-output (IO) benchmark matrices from the US Bureau of Economic</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>(Figures 6 and 7) require the shared BEA-to-Sraffa pipeline and are</t>
+          <t>Analysis (BEA) for 2002 and 2007.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>deferred to v1.1 alongside XS2001.</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>For v1.0, XS2101 ships the verbatim named summary statistics quoted in</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>paper Section 5 (p. 272) — the shipped `statistic` column carries</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>`avg_CI_lower_bound`/`avg_CI_upper_bound`, `n_prices_switching_value`(_pct),</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CI &lt; 0.1 across all aggregations is the paper's headline empirical</t>
+          <t>`n_prices_switching_bienenfeld`(_pct), and `max_bienenfeld_deviation_pct`</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>finding: Sraffa price curves are nearly linear, validating Bienenfeld's</t>
+          <t>(no Theil statistic is present). The full ~295-point CI and label-switching</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>(1988) linear approximation. The fact that only 6% of 2002 prices</t>
+          <t>scatters (Figures 6 and 7) require the shared BEA-to-Sraffa pipeline and are</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>switch labor-value sign, and only 1% switch the Bienenfeld line (none</t>
+          <t>deferred to v1.1 alongside XS2001.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>with &gt;1% deviation), is independent confirmation of the Sraffa</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stochastic Effect already shown in XS2001 at the aggregate level.</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
@@ -1433,109 +1433,117 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>CI &lt; 0.1 across all aggregations is the paper's headline empirical</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>finding: Sraffa price curves are nearly linear, validating Bienenfeld's</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>(1988) linear approximation. The fact that only 6% of 2002 prices</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>switch labor-value sign, and only 1% switch the Bienenfeld line (none</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| XS2101-A | 2002, 2007 | Paper Section 5 (p. 272) verbatim summary statistics | dimensionless / counts / percent | `SalvagedInputs/book_data/Reconstructed/XS2101_summary_statistics.csv` |</t>
+          <t>with &gt;1% deviation), is independent confirmation of the Sraffa</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Stochastic Effect already shown in XS2001 at the aggregate level.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Underlying primary data: BEA Benchmark IO 1977/1982/1987/1992/1997/2002/</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2007 detailed tables; BLS Employment Projections industry data for</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>skill-adjusted labor coefficients. Shared with XS2001 (v1.1 pipeline).</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>| XS2101-A | 2002, 2007 | Paper Section 5 (p. 272) verbatim summary statistics | dimensionless / counts / percent | reconstructed CSV |</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>`derived` — v1.0 verbatim transcription of summary statistics. v1.1 will</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>recompute the full 295-matrix CI distribution.</t>
+          <t>Underlying primary data: BEA Benchmark IO 1977/1982/1987/1992/1997/2002/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2007 detailed tables; US Bureau of Labor Statistics (BLS) Employment</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>Projections industry data for skill-adjusted labor coefficients. Shared</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>with XS2001 (v1.1 pipeline).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2002 and 2007 (the two benchmark years for which CI/Theil distributions</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>are computed in the paper).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -1545,24 +1553,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>`derived` — v1.0 verbatim transcription of summary statistics. v1.1 will</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>recompute the full 295-matrix CI distribution.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Mixed per row: dimensionless (CI averages), count (n_prices), percent</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>(switching shares, Bienenfeld max deviation).</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
@@ -1572,59 +1580,51 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>2002 and 2007 (the two benchmark years for which the CI and</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>label-switching distributions are computed in the paper).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1. **Full distribution NOT computed in v1.0.** Figures 6 and 7</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   require the shared BEA-to-Sraffa pipeline deferred to v1.1.</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2. The "295 matrices" total = 176 (2002 aggregation levels) + 119</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (2007 aggregation levels) per paper Appendix 1; this is a</t>
+          <t>Mixed per row: dimensionless (CI averages), count (n_prices), percent</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   methodology constant, not a data point.</t>
+          <t>(switching shares, Bienenfeld max deviation).</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>3. BLS sect300.xls crosswalk URL (paper-cited) is 403; v1.1 must</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">   locate current BLS Employment Projections industry data successor.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -1634,41 +1634,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>1. **Full distribution NOT computed in v1.0.** Figures 6 and 7</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   require the shared BEA-to-Sraffa pipeline deferred to v1.1.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- Dossier: `Technical/research/XS2101_research.json`</t>
+          <t>2. The "295 matrices" total = 176 (2002 aggregation levels) + 119</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- Companion: `XS2001` (Shaikh 2020 aggregate ratios) — shares BEA-to-Sraffa pipeline</t>
+          <t xml:space="preserve">   (2007 aggregation levels) per paper Appendix 1; this is a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- Reconstructed: `SalvagedInputs/book_data/Reconstructed/XS2101_summary_statistics.csv`</t>
+          <t xml:space="preserve">   methodology constant, not a data point.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3. BLS sect300.xls crosswalk URL (paper-cited) is 403; v1.1 must</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t xml:space="preserve">   locate current BLS Employment Projections industry data successor.</t>
         </is>
       </c>
     </row>
@@ -1678,78 +1686,74 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- Companion: `XS2001` (Shaikh 2020 aggregate ratios) — shares the BEA-to-Sraffa pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>- Tolerance: 0.5% (verbatim transcription of named summary stats).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4">
+    <row r="88">
+      <c r="A88" s="4">
         <f>== EPR: XS2101_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t># XS2101 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>**Series**: XS2101 — Sraffa Curvature Index Summary</t>
         </is>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Construction**: `derived` (verbatim summary stats in v1.0; pipeline-derived in v1.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>## 1. v1.0 scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Verbatim Section 5 (p. 272) summary statistics for 2002 and 2007 BEA</t>
+          <t>**Construction**: `derived` (verbatim summary stats in v1.0; pipeline-derived in v1.1)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>benchmark IO matrices.</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1763,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>## 2. v1.1 plan</t>
+          <t>## 1. v1.0 scope</t>
         </is>
       </c>
     </row>
@@ -1769,100 +1773,100 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Shared BEA-to-Sraffa pipeline with XS2001 (see XS2001_EPR §3). v1.1</t>
+          <t>Verbatim Section 5 (p. 272) summary statistics for the 2002 and 2007</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>implementation regenerates:</t>
+          <t>benchmark input-output (IO) matrices from the US Bureau of Economic</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Analysis (BEA).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>- 295 aggregated A matrices for 2002 (176 levels) + 2007 (119 levels)</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>- Per-matrix Sraffa price curves p(r) at 21 sample points</t>
+          <t>## 2. v1.1 plan</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>- Per-matrix Curvature Index CI = 1 - SI (Bienenfeld-line vs arc length)</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>- Per-matrix Theil indexes</t>
+          <t>Shared BEA-to-Sraffa pipeline with XS2001 (see the XS2001 Extension</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>- Full reconstruction of Figures 6 and 7 scatters</t>
+          <t>Provenance Record §3). v1.1 implementation regenerates:</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>- Extension to BEA Benchmark IO 2012 and 2017 (subject to NAICS</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">  bridging documentation in EPR addendum)</t>
+          <t>- 295 aggregated A matrices for 2002 (176 levels) + 2007 (119 levels)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>- Per-matrix Sraffa price curves p(r) at 21 sample points</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>## 3. Proxies</t>
+          <t>- Per-matrix Curvature Index CI = 1 - SI (Bienenfeld-line vs arc length)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>- Per-matrix Theil indexes</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BLS sect300.xls crosswalk URL is 403 (paper-cited). v1.1 substitutes</t>
+          <t>- Full reconstruction of Figures 6 and 7 scatters</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>current BLS Employment Projections industry data; this is a URL</t>
+          <t>- Extension to BEA Benchmark IO 2012 and 2017 (subject to NAICS</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>migration within an active domain, NOT a data-source proxy.</t>
+          <t xml:space="preserve">  bridging documentation in EPR addendum)</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1876,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>## 4. Synthetic data</t>
+          <t>## 3. Proxies</t>
         </is>
       </c>
     </row>
@@ -1882,203 +1886,244 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>None. v1.0 is verbatim transcription.</t>
+          <t>The US Bureau of Labor Statistics (BLS) sect300.xls crosswalk URL is 403</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>(paper-cited). v1.1 substitutes current BLS Employment Projections</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>## 5. Conceptual continuity vs adjacent concepts</t>
+          <t>industry data; this is a URL migration within an active domain, not a</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>data-source proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline + extended</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BLS Employment Projections crosswalk) measures `Sraffa Curvature Index</t>
+          <t>## 4. Synthetic data</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>distribution across aggregation levels` rather than `single-matrix CI</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>point estimates` or `Theil price-value dispersion alone` because:</t>
+          <t>None. v1.0 is verbatim transcription.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>- Source agency choice: BEA Benchmark IO at the 176/119-order detail is</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the only published US matrix that supports the 295-aggregation rollup.</t>
+          <t>## 5. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  No alternative agency provides comparable industry detail.</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>- Methodology continuity: v1.0 verbatim summary stats and v1.1 full CI</t>
+          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline + extended</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">  distribution both apply Bienenfeld-line vs arc-length per p(r) curve.</t>
+          <t>BLS Employment Projections crosswalk) measures `Sraffa Curvature Index</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Adding 2012/2017 benchmark matrices reuses the same CI = 1 − SI</t>
+          <t>distribution across aggregation levels` rather than `single-matrix CI</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">  estimator, not a substitute.</t>
+          <t>point estimates` or `Theil price-value dispersion alone` because:</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>- Disambiguation: Curvature Index (CI &lt; 0.1) is NOT the price-value</t>
+          <t>- Source agency choice: BEA Benchmark IO at the 176/119-order detail is</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ratio of XS2001 — CI characterizes the *shape* of p(r) over r ∈ [0, R],</t>
+          <t xml:space="preserve">  the only published US matrix that supports the 295-aggregation rollup.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">  while XS2001 reports the scalar p(r_obs)/v aggregate. Both belong to</t>
+          <t xml:space="preserve">  No alternative agency provides comparable industry detail.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the same Sraffa-stochastic-effect evidence base but answer different</t>
+          <t>- Methodology continuity: v1.0 verbatim summary stats and v1.1 full CI</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">  questions and have different content_type tags.</t>
+          <t xml:space="preserve">  distribution both apply Bienenfeld-line vs arc-length per p(r) curve.</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Adding 2012/2017 benchmark matrices reuses the same CI = 1 − SI</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>The book's original concept (Shaikh-Coronado-Nassif-Pires 2020 §5, p. 272)</t>
+          <t xml:space="preserve">  estimator, not a substitute.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>was: "Sraffa price curves are close to linear" — operationalized as</t>
+          <t>- Disambiguation: Curvature Index (CI &lt; 0.1) is NOT the price-value</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CI &lt; 0.1 across all 295 aggregations and only 6% labor-value sign</t>
+          <t xml:space="preserve">  ratio of XS2001 — CI characterizes the *shape* of p(r) over r ∈ [0, R],</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>switches in 2002. The modern series preserves the CI estimator and</t>
+          <t xml:space="preserve">  while XS2001 reports the scalar p(r_obs)/v aggregate. Both belong to</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>aggregation-level rollup methodology while permitting the BLS</t>
+          <t xml:space="preserve">  the same Sraffa-stochastic-effect evidence base but answer different</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Employment Projections crosswalk URL migration (sect300.xls → current</t>
+          <t xml:space="preserve">  questions and have different content_type tags.</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>EP industry data; same agency, current URL). This is NOT a proxy</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>substitution forbidden by the No-Proxy rule because (a) BEA IO is the</t>
+          <t>The book's original concept (Shaikh-Coronado-Nassif-Pires 2020 §5, p. 272)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>same source family, (b) BLS Employment Projections is the same agency</t>
+          <t>was: "Sraffa price curves are close to linear" — operationalized as</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
+        <is>
+          <t>CI &lt; 0.1 across all 295 aggregations and only 6% labor-value sign</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>switches in 2002. The modern series preserves the CI estimator and</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>aggregation-level rollup methodology while permitting the BLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Employment Projections crosswalk URL migration (sect300.xls → current</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>EP industry data; same agency, current URL). This is not a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>substitution because (a) BEA IO is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>same source family, (b) BLS Employment Projections is the same agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>under a renamed program — concept-identical labor input data.</t>
         </is>
@@ -2589,7 +2634,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2698,7 +2743,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T22:52:29.222860+00:00</t>
+          <t>2026-07-02T06:28:59.373508+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS2101_extenbook.xlsx
+++ b/extenbooks/XS2101_extenbook.xlsx
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:28:59.373508+00:00</t>
+          <t>2026-07-11T03:44:27.719459+00:00</t>
         </is>
       </c>
     </row>
@@ -2758,11 +2758,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2785,6 +2785,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>study_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>study_replication</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Verbatim headline summary statistics from Section 5 (p.272) of Shaikh, Coronado &amp; Nassif-Pires (2020): average curvature-index bounds, total price count, and the value-line / Bienenfeld-line switching counts and shares. Few points is legitimate (these ARE the study's full reported summary stats, not a truncated series). The prescreen MIXED_UNITS flag is real and is resolved by per-subseries units (dimensionless CI bounds, count price tallies, percent switching shares) so each statistic renders on its own scale rather than being mixed on one axis. SPARSE flag is a true-positive but acceptable: the CI bounds span both benchmark years (2002, 2007); the switching statistics are reported for 2002 only (the 425-price benchmark), faithful to the paper.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2101_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2101_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Decision 0001: ES placeholder. Phase 3 subagent must read the paper PDF, identify empirical figures, and either populate this placeholder as a single series OR expand to N series ES{group}01..ES{group}NN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
